--- a/Gravedigger2026/Assets/ConfigTables/Excel/战斗_阵容羁绊配置表_Combat_FormationBondConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/战斗_阵容羁绊配置表_Combat_FormationBondConfig.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -419,48 +419,76 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>羁绊ID</t>
+          <t>BondId</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>羁绊等级</t>
+          <t>BondLevel</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>羁绊名称</t>
+          <t>DisplayName</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>羁绊图标</t>
+          <t>IconAssetId</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>羁绊介绍</t>
+          <t>Description</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>羁绊激活条件</t>
+          <t>ActivationCondition</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>羁绊Buff</t>
+          <t>BondBuff</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>（待补 SPEC 中文说明）BondId</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>（待补 SPEC 中文说明）BondLevel</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>（待补 SPEC 中文说明）DisplayName</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>（待补 SPEC 中文说明）IconAssetId</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>（待补 SPEC 中文说明）Description</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>（待补 SPEC 中文说明）ActivationCondition</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>（待补 SPEC 中文说明）BondBuff</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -505,8 +533,10 @@
           <t>Bond_Demo</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>1</v>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/Gravedigger2026/Assets/ConfigTables/Excel/战斗_阵容羁绊配置表_Combat_FormationBondConfig.xlsx
+++ b/Gravedigger2026/Assets/ConfigTables/Excel/战斗_阵容羁绊配置表_Combat_FormationBondConfig.xlsx
@@ -419,74 +419,74 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>BondId</t>
+          <t>羁绊ID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>BondLevel</t>
+          <t>羁绊等级</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>DisplayName</t>
+          <t>羁绊名称</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>IconAssetId</t>
+          <t>羁绊图标</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>羁绊介绍</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>ActivationCondition</t>
+          <t>羁绊激活条件</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>BondBuff</t>
+          <t>羁绊Buff</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>（待补 SPEC 中文说明）BondId</t>
+          <t>复合主键之一</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>（待补 SPEC 中文说明）BondLevel</t>
+          <t>复合主键之一；≥1；同 Id 多等级互斥（规则见 §3.17）</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>（待补 SPEC 中文说明）DisplayName</t>
+          <t>UI 展示</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>（待补 SPEC 中文说明）IconAssetId</t>
+          <t>运行时 Resources/UI/Bonds/{IconAssetId}；缺图占位</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>（待补 SPEC 中文说明）Description</t>
+          <t>UI 只读；不作效果器</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>（待补 SPEC 中文说明）ActivationCondition</t>
+          <t>结构化 DSL（§3.17）；加载期校验</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>（待补 SPEC 中文说明）BondBuff</t>
+          <t>FK → SkillEffectConfig.SkillEffectId</t>
         </is>
       </c>
     </row>
